--- a/docs/Check.xlsx
+++ b/docs/Check.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D549F6AE-A299-4BE0-BE85-A0172FB5B572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB738FE-3FF2-4172-982B-6A8CFF38AE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="204" yWindow="1176" windowWidth="21600" windowHeight="11232" xr2:uid="{CC27895C-042D-446B-AA3B-A5E466A6E324}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CC27895C-042D-446B-AA3B-A5E466A6E324}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Terminal</t>
   </si>
@@ -68,18 +68,12 @@
     <t>40 HQ</t>
   </si>
   <si>
-    <t>20 RF</t>
-  </si>
-  <si>
     <t>20 UT</t>
   </si>
   <si>
     <t>40 UT</t>
   </si>
   <si>
-    <t>40 RF</t>
-  </si>
-  <si>
     <t>STATUS F/E</t>
   </si>
   <si>
@@ -96,6 +90,18 @@
   </si>
   <si>
     <t>A3 (C1,C2) (Hutchison Laemchabang Terminal Limited, HLT)</t>
+  </si>
+  <si>
+    <t>20 RH</t>
+  </si>
+  <si>
+    <t>40 RH</t>
+  </si>
+  <si>
+    <t>20 FR</t>
+  </si>
+  <si>
+    <t>40 FR</t>
   </si>
 </sst>
 </file>
@@ -190,10 +196,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -530,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9150FB13-47E0-4737-B7F2-1D814CFA1FE2}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.8984375" customWidth="1"/>
@@ -546,27 +552,27 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
+      <c r="A2" s="4"/>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3"/>
+      <c r="A3" s="4"/>
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
+      <c r="A4" s="4"/>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
+      <c r="A5" s="3"/>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -578,72 +584,84 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3"/>
+      <c r="A8" s="4"/>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3"/>
+      <c r="A9" s="4"/>
       <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="1" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3"/>
-      <c r="B12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
+      <c r="A13" s="4"/>
       <c r="B13" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
       <c r="B14" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="4"/>
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3"/>
+      <c r="B16" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3"/>
+      <c r="B18" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="A17:A18"/>
     <mergeCell ref="A1:A5"/>
+    <mergeCell ref="A6:A16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/Check.xlsx
+++ b/docs/Check.xlsx
@@ -1,132 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nirisara\Desktop\Workshop AI\SHORE\input\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB738FE-3FF2-4172-982B-6A8CFF38AE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CC27895C-042D-446B-AA3B-A5E466A6E324}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>Terminal</t>
-  </si>
-  <si>
-    <t>LCMT Company LTD, ( under LCB1 Group)  A0</t>
-  </si>
-  <si>
-    <t>ESCO (EASTERN SEA LCH CNTR TML/B3)</t>
-  </si>
-  <si>
-    <t>A2 ( Thai Laemchabang Terminal, TLT / 허치슨 )</t>
-  </si>
-  <si>
-    <t>B5/C3 LCIT (LAEM CHABANG INTERNATIONAL TERMINAL CO., LTD)</t>
-  </si>
-  <si>
-    <t>SIZE</t>
-  </si>
-  <si>
-    <t>20 GP</t>
-  </si>
-  <si>
-    <t>40 GP</t>
-  </si>
-  <si>
-    <t>40 HQ</t>
-  </si>
-  <si>
-    <t>20 UT</t>
-  </si>
-  <si>
-    <t>40 UT</t>
-  </si>
-  <si>
-    <t>STATUS F/E</t>
-  </si>
-  <si>
-    <t>FULL</t>
-  </si>
-  <si>
-    <t>EMPTY</t>
-  </si>
-  <si>
-    <t>20 TK</t>
-  </si>
-  <si>
-    <t>40 TK</t>
-  </si>
-  <si>
-    <t>A3 (C1,C2) (Hutchison Laemchabang Terminal Limited, HLT)</t>
-  </si>
-  <si>
-    <t>20 RH</t>
-  </si>
-  <si>
-    <t>40 RH</t>
-  </si>
-  <si>
-    <t>20 FR</t>
-  </si>
-  <si>
-    <t>40 FR</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Tahoma"/>
+      <charset val="222"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-      <charset val="222"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -186,36 +94,109 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -535,133 +516,171 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9150FB13-47E0-4737-B7F2-1D814CFA1FE2}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="10.8984375" customWidth="1"/>
-    <col min="2" max="2" width="59.59765625" customWidth="1"/>
+    <col width="10.8984375" customWidth="1" min="1" max="1"/>
+    <col width="59.59765625" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3"/>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="3"/>
-      <c r="B16" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="1" t="s">
-        <v>13</v>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LCMT Company LTD, ( under LCB1 Group)  A0</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="n"/>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>ESCO (EASTERN SEA LCH CNTR TML/B3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>B5/C3 LCIT (LAEM CHABANG INTERNATIONAL TERMINAL CO., LTD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>A3 (C1,C2) (Hutchison Laemchabang Terminal Limited, HLT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SIZE</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>20 GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>40 GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>40 HQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>20 RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>40 RH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>20 UT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>40 UT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>20 TK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>40 TK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>20 FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>40 FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>STATUS F/E</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A1:A5"/>
-    <mergeCell ref="A6:A16"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="A5:A15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
